--- a/mau/Mau-ngan-hang-cau-hoi.xlsx
+++ b/mau/Mau-ngan-hang-cau-hoi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t xml:space="preserve">STT</t>
   </si>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">Cách điền</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi dòng ở trang «Câu hỏi» là một câu hỏi. Các dòng ví dụ (dòng nền vàng là đoạn dẫn) cho thấy cách ghi mọi loại câu — xoá chúng trước khi soạn. Giữ nguyên dòng tiêu đề (có thể đổi thứ tự cột hoặc thêm cột riêng, cột lạ được bỏ qua).</t>
+    <t xml:space="preserve">Mỗi dòng ở trang «Câu hỏi» là một câu hỏi. Các dòng 2–18 là ví dụ đủ mọi loại câu (dòng nền vàng là đoạn dẫn): xem xong thì chọn các dòng đó → chuột phải → Delete (Xoá) — ảnh ví dụ bị xoá theo. Giữ nguyên dòng tiêu đề (đổi thứ tự cột hay thêm cột riêng đều được, cột lạ được bỏ qua).</t>
   </si>
   <si>
     <t xml:space="preserve">1. CÁCH DÙNG</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">Bước 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Lưu tệp, mở công cụ Ngân hàng câu hỏi Canvas, kéo thả tệp Excel vào (kèm các ảnh ghi ở cột Ảnh nếu có). Soát lại từng câu: câu báo đỏ không được xuất.</t>
+    <t xml:space="preserve">Lưu tệp dạng Excel (.xlsx), mở công cụ Ngân hàng câu hỏi Canvas, kéo thả tệp vào (kèm các ảnh ghi ở cột Ảnh nếu có). Soát lại từng câu: câu báo đỏ không được xuất.</t>
   </si>
   <si>
     <t xml:space="preserve">Bước 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Bấm Tải gói QTI rồi nhập vào Canvas — New Quizzes: Item Banks → ⋮ → Import Content; Classic Quizzes: Settings → Import Course Content → QTI .zip file.</t>
+    <t xml:space="preserve">Bấm Tải gói QTI rồi làm theo hướng dẫn hiện ngay dưới nút. New Quizzes (khuyên dùng): Ngân Hàng Câu Hỏi (Item Banks) → mở một ngân hàng còn trống → ⋮ → Import Content. Classic Quizzes: Cài Đặt → Nhập Nội Dung Khóa Học (Settings → Import Course Content) → Tập tin .zip QTI.</t>
   </si>
   <si>
     <t xml:space="preserve">2. CÁC CỘT CỦA TRANG «CÂU HỎI»</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">Có</t>
   </si>
   <si>
-    <t xml:space="preserve">Tên tệp ảnh (nhiều ảnh ngăn bằng ;) — khi nạp, kéo thả kèm các ảnh đó. Hoặc dán ảnh thẳng lên trang tính, đặt trên đúng dòng câu hỏi (như câu 2 ví dụ).</t>
+    <t xml:space="preserve">Tên tệp ảnh (nhiều ảnh ngăn bằng ;) — khi nạp, kéo thả kèm các ảnh đó. Hoặc dán ảnh thẳng lên trang tính sao cho góc trên bên trái của ảnh nằm trong dòng câu hỏi (như câu 2 ví dụ), hoặc Insert → Pictures → Place in Cell (Chèn → Ảnh → Đặt trong ô). Ảnh ở cột A…H thuộc phương án đó, ở cột Lời giải thuộc lời giải.</t>
   </si>
   <si>
     <t xml:space="preserve">hinh-cau-3.png</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">A … H</t>
   </si>
   <si>
-    <t xml:space="preserve">TN, NĐ: các phương án. ĐS: các ý a, b, c, d (cột A–D). GHÉP: mỗi ô một cặp “trái =&gt; phải”. Có thể đánh dấu * trước phương án đúng thay cho cột Đáp án.</t>
+    <t xml:space="preserve">TN, NĐ: các phương án. ĐS: các ý a, b, c, d (cột A–D). GHÉP: mỗi ô một cặp “trái =&gt; phải”. Có thể đánh dấu * trước phương án đúng thay cho cột Đáp án. Các cột này và cột Đáp án đã đặt sẵn kiểu Văn bản (Text) để Excel không tự đổi 1/2 thành ngày tháng.</t>
   </si>
   <si>
     <t xml:space="preserve">*Hà Nội</t>
@@ -599,36 +599,39 @@
     <t xml:space="preserve">ĐSĐS  hoặc  a-Đ, b-S, c-Đ, d-S</t>
   </si>
   <si>
+    <t xml:space="preserve">Multiple Dropdowns (hoặc tách thành các câu Đúng/Sai)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không dùng cột A–H.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Các cách viết đúng ngăn bằng dấu ; ví dụ 8/3; 2,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short Answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,5  hoặc  12,5 ± 0,1  hoặc  khoảng 1,5 .. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numerical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ô [[đáp án]] trong nội dung; nhiều cách viết: [[8/3|2,67]].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để trống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill In Multiple Blanks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ô [[sai|*đúng|sai]] trong nội dung, dấu * trước lựa chọn đúng.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Multiple Dropdowns</t>
   </si>
   <si>
-    <t xml:space="preserve">Không dùng cột A–H.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Các cách viết đúng ngăn bằng dấu ; ví dụ 8/3; 2,67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short Answer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,5  hoặc  12,5 ± 0,1  hoặc  khoảng 1,5 .. 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numerical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ô [[đáp án]] trong nội dung; nhiều cách viết: [[8/3|2,67]].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Để trống</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill In Multiple Blanks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ô [[sai|*đúng|sai]] trong nội dung, dấu * trước lựa chọn đúng.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mỗi ô A–H một cặp “trái =&gt; phải”. Ô không có =&gt; (hoặc ghi “Nhiễu: x; y”) là vế phải gây nhiễu.</t>
   </si>
   <si>
@@ -659,13 +662,19 @@
     <t xml:space="preserve">Công thức</t>
   </si>
   <si>
-    <t xml:space="preserve">Gõ LaTeX giữa hai dấu $, ví dụ $\frac{1}{2}$, $\sqrt{x+1}$, $x^2$, $\vec{a}$, $\int_0^1 f(x)\,dx$, $\begin{cases} x+y=3\\ x-y=1 \end{cases}$ — công cụ tự chuyển thành công thức trên Canvas.</t>
+    <t xml:space="preserve">Gõ LaTeX giữa hai dấu $, ví dụ $\frac{1}{2}$, $\sqrt{x+1}$, $x^2$, $\vec{a}$, $\int_0^1 f(x)\,dx$, $\begin{cases} x+y=3\\ x-y=1 \end{cases}$ — công cụ tự chuyển thành công thức trên Canvas. Không dùng Equation, Text Box hay Shapes của Excel: công cụ không đọc được (sẽ báo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân số, ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ở cột không đặt kiểu Văn bản (Nội dung, Lời giải, Điểm…), gõ riêng 1/2 hay 8/3 thì Excel tự đổi thành ngày tháng và công cụ sẽ báo lỗi: gõ thêm dấu nháy đơn phía trước ('1/2) hoặc định dạng ô là Văn bản (Text). Ô định dạng % hay Phân số (Fraction) được đọc như Excel hiển thị.</t>
   </si>
   <si>
     <t xml:space="preserve">Số thập phân</t>
   </si>
   <si>
-    <t xml:space="preserve">Viết bằng dấu phẩy như thường lệ (2,5). Riêng câu SỐ, khi làm bài trên Canvas học sinh gõ dấu chấm (2.5).</t>
+    <t xml:space="preserve">Viết bằng dấu phẩy như thường lệ (2,5). Câu SỐ: Canvas chỉ hiểu dấu chấm nên học sinh phải gõ 2.5 — hãy nhắc trong đề; muốn chấm đúng cả 2,5 lẫn 2.5 thì dùng loại TLN.</t>
   </si>
   <si>
     <t xml:space="preserve">Dùng ảnh PNG hoặc JPG. Không dùng ảnh EMF, WMF, SVG — Canvas không hiển thị được.</t>
@@ -674,13 +683,19 @@
     <t xml:space="preserve">Ô gộp</t>
   </si>
   <si>
-    <t xml:space="preserve">Ô gộp ở các cột Loại câu, Điểm, Ngân hàng, Mức độ, Chủ đề được hiểu cho mọi dòng trong vùng gộp.</t>
+    <t xml:space="preserve">Ô gộp ở các cột Loại câu, Điểm, Ngân hàng, Mức độ, Chủ đề được hiểu cho mọi dòng trong vùng gộp. Không gộp ô ở cột Nội dung, A…H, Đáp án.</t>
   </si>
   <si>
     <t xml:space="preserve">Đúng/Sai</t>
   </si>
   <si>
     <t xml:space="preserve">Canvas chấm câu Đúng/Sai theo từng ý (mỗi ý đúng = điểm câu ÷ số ý); thang 0,1 – 0,25 – 0,5 – 1 điểm của Bộ GD&amp;ĐT không áp dụng được.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lưu tệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lưu dạng Excel Workbook (.xlsx). Tệp .xls cũ, .csv hay Google Sheets: mở rồi lưu (hoặc tải về) dạng .xlsx trước khi nạp.</t>
   </si>
 </sst>
 </file>
@@ -798,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,6 +851,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -847,14 +883,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1828800" cy="1371600"/>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1428750</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Hình 1" descr="Đồ thị hàm số y = f(x): đi lên đến điểm (−1; 2), đi xuống đến điểm (1; −2) rồi đi lên."/>
@@ -879,7 +920,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -891,24 +932,24 @@
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="15" width="44" customWidth="1"/>
-    <col min="16" max="16" width="23" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="1" max="1" width="6" style="15" customWidth="1"/>
+    <col min="2" max="2" width="21" style="15" customWidth="1"/>
+    <col min="3" max="3" width="58" style="10" customWidth="1"/>
+    <col min="4" max="4" width="29" style="10" customWidth="1"/>
+    <col min="5" max="5" width="22" style="13" customWidth="1"/>
+    <col min="6" max="6" width="22" style="13" customWidth="1"/>
+    <col min="7" max="7" width="22" style="13" customWidth="1"/>
+    <col min="8" max="8" width="22" style="13" customWidth="1"/>
+    <col min="9" max="9" width="13" style="13" customWidth="1"/>
+    <col min="10" max="10" width="13" style="13" customWidth="1"/>
+    <col min="11" max="11" width="13" style="13" customWidth="1"/>
+    <col min="12" max="12" width="13" style="13" customWidth="1"/>
+    <col min="13" max="13" width="15" style="14" customWidth="1"/>
+    <col min="14" max="14" width="7" style="15" customWidth="1"/>
+    <col min="15" max="15" width="44" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23" style="10" customWidth="1"/>
+    <col min="17" max="17" width="9" style="15" customWidth="1"/>
+    <col min="18" max="18" width="18" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="33" customHeight="1">
@@ -978,23 +1019,23 @@
         <v>19</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3" t="s">
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="17" t="s">
         <v>4</v>
       </c>
       <c r="N2" s="3">
@@ -1024,23 +1065,23 @@
         <v>28</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="3" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="17" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="3">
@@ -1070,23 +1111,23 @@
         <v>36</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="3" t="s">
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="17" t="s">
         <v>41</v>
       </c>
       <c r="N4" s="3">
@@ -1114,15 +1155,15 @@
         <v>46</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="19"/>
       <c r="N5" s="5"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
@@ -1142,23 +1183,23 @@
         <v>47</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="3" t="s">
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="17" t="s">
         <v>6</v>
       </c>
       <c r="N6" s="3">
@@ -1186,23 +1227,23 @@
         <v>53</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="3" t="s">
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="17" t="s">
         <v>6</v>
       </c>
       <c r="N7" s="3">
@@ -1230,15 +1271,15 @@
         <v>59</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="19"/>
       <c r="N8" s="5"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4" t="s">
@@ -1258,23 +1299,23 @@
         <v>61</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="3" t="s">
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="17" t="s">
         <v>66</v>
       </c>
       <c r="N9" s="3">
@@ -1304,15 +1345,15 @@
         <v>70</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="3" t="s">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="17" t="s">
         <v>71</v>
       </c>
       <c r="N10" s="3">
@@ -1342,15 +1383,15 @@
         <v>75</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="3" t="s">
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17" t="s">
         <v>76</v>
       </c>
       <c r="N11" s="3">
@@ -1380,15 +1421,15 @@
         <v>79</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="3" t="s">
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17" t="s">
         <v>80</v>
       </c>
       <c r="N12" s="3">
@@ -1418,15 +1459,15 @@
         <v>84</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="3" t="s">
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17" t="s">
         <v>85</v>
       </c>
       <c r="N13" s="3">
@@ -1456,15 +1497,15 @@
         <v>89</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="3"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="17"/>
       <c r="N14" s="3">
         <v>0.5</v>
       </c>
@@ -1492,15 +1533,15 @@
         <v>94</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="3"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="17"/>
       <c r="N15" s="3">
         <v>0.5</v>
       </c>
@@ -1526,23 +1567,23 @@
         <v>96</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="3"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="17"/>
       <c r="N16" s="3">
         <v>1</v>
       </c>
@@ -1568,23 +1609,23 @@
         <v>102</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="3" t="s">
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="17" t="s">
         <v>5</v>
       </c>
       <c r="N17" s="3">
@@ -1614,15 +1655,15 @@
         <v>108</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="3" t="s">
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="17" t="s">
         <v>109</v>
       </c>
       <c r="N18" s="3">
@@ -1648,7 +1689,7 @@
       <formula1>"NB,TH,VD,VDC"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Nội dung câu hỏi" prompt="Xuống dòng: Alt + Enter. Công thức: $x^2$, $\frac{1}{2}$. Ô điền: [[đáp án]]. Ô chọn: [[sai|*đúng|sai]]." sqref="C2:C1000"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Phương án / ý / cặp ghép" prompt="TN, NĐ: phương án. ĐS: các ý a, b, c, d. GHÉP: trái =&gt; phải (ô không có =&gt; hoặc ghi Nhiễu: x; y là vế phải gây nhiễu)." sqref="E2:L1000"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Phương án / ý / cặp ghép" prompt="TN, NĐ: phương án (có thể ghi * trước phương án đúng). ĐS: các ý a, b, c, d. GHÉP: trái =&gt; phải; ô không có =&gt; hoặc ghi Nhiễu: x; y là vế phải gây nhiễu." sqref="E2:L1000"/>
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Đáp án" prompt="TN: B · NĐ: A, C · ĐS: ĐSĐS · TLN: 8/3; 2,67 · SỐ: 12,5 hoặc 12,5 ± 0,1 hoặc 1,5 .. 2 · ĐIỀN, CHỌN, GHÉP: để trống." sqref="M2:M1000"/>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -1668,7 +1709,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1693,7 +1734,7 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="49" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>112</v>
       </c>
@@ -1742,7 +1783,7 @@
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="49" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>121</v>
       </c>
@@ -1817,7 +1858,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" ht="49">
+    <row r="16" ht="79">
       <c r="A16" s="11" t="s">
         <v>3</v>
       </c>
@@ -1831,7 +1872,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" ht="49">
+    <row r="17" ht="64">
       <c r="A17" s="11" t="s">
         <v>137</v>
       </c>
@@ -1980,7 +2021,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="29" ht="34">
+    <row r="29" ht="64">
       <c r="A29" s="11" t="s">
         <v>60</v>
       </c>
@@ -2047,7 +2088,7 @@
         <v>170</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" ht="34">
@@ -2055,13 +2096,13 @@
         <v>95</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>170</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" ht="34">
@@ -2069,13 +2110,13 @@
         <v>83</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" ht="34">
@@ -2083,76 +2124,96 @@
         <v>45</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37"/>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" ht="34" customHeight="1">
+    <row r="39" ht="49" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10"/>
     </row>
-    <row r="40" ht="19" customHeight="1">
+    <row r="40" ht="49" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
     </row>
-    <row r="41" ht="19" customHeight="1">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
     </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:D3"/>
@@ -2169,8 +2230,13 @@
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="37" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>